--- a/results/MC_Dist=Exp_n=500_LT=0.1_C=0.2_B=100.xlsx
+++ b/results/MC_Dist=Exp_n=500_LT=0.1_C=0.2_B=100.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -123,13 +123,16 @@
     <t xml:space="preserve">Gamma</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5,1</t>
+    <t xml:space="preserve">1,0.8</t>
   </si>
   <si>
     <t xml:space="preserve">x1.mean</t>
   </si>
   <si>
     <t xml:space="preserve">x1.sd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8</t>
   </si>
   <si>
     <t xml:space="preserve">x2.mean</t>
@@ -545,22 +548,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.03874718531109</v>
+        <v>-1.01398189286358</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0387471853110939</v>
+        <v>-0.0139818928635769</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01727340969818</v>
+        <v>0.0179660524158753</v>
       </c>
       <c r="E2" t="n">
-        <v>0.126219567103703</v>
+        <v>0.133977832810781</v>
       </c>
       <c r="F2" t="n">
-        <v>0.94</v>
+        <v>0.97</v>
       </c>
       <c r="G2" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -568,22 +571,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>-1.02065719556149</v>
+        <v>-0.982931159183058</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0206571955614872</v>
+        <v>0.0170688408169419</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0122846690699449</v>
+        <v>0.0108403538204916</v>
       </c>
       <c r="E3" t="n">
-        <v>0.109442800620027</v>
+        <v>0.103225792004748</v>
       </c>
       <c r="F3" t="n">
         <v>0.94</v>
       </c>
       <c r="G3" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="4">
@@ -591,22 +594,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>1.55013838315465</v>
+        <v>1.02000010933636</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0501383831546531</v>
+        <v>0.0200001093363602</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0216342090440928</v>
+        <v>0.016224610974175</v>
       </c>
       <c r="E4" t="n">
-        <v>0.138972970189032</v>
+        <v>0.126429629089968</v>
       </c>
       <c r="F4" t="n">
-        <v>0.94</v>
+        <v>0.95</v>
       </c>
       <c r="G4" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="5">
@@ -614,22 +617,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>1.20121709879652</v>
+        <v>0.955310838256851</v>
       </c>
       <c r="C5" t="n">
-        <v>0.201217098796524</v>
+        <v>0.155310838256851</v>
       </c>
       <c r="D5" t="n">
-        <v>0.101956535553837</v>
+        <v>0.0910263764734371</v>
       </c>
       <c r="E5" t="n">
-        <v>0.249176856395976</v>
+        <v>0.259962934408065</v>
       </c>
       <c r="F5" t="n">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="G5" t="n">
-        <v>0.94</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="6">
@@ -637,22 +640,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>2.01132465275127</v>
+        <v>2.00298687860373</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0113246527512656</v>
+        <v>0.00298687860373326</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00246513103095295</v>
+        <v>0.00283261140126661</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0485848551767073</v>
+        <v>0.0534061052526369</v>
       </c>
       <c r="F6" t="n">
-        <v>0.92</v>
+        <v>0.99</v>
       </c>
       <c r="G6" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
     </row>
   </sheetData>
@@ -783,20 +786,20 @@
         <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
         <v>7</v>
@@ -815,2325 +818,2325 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-1.09972548715933</v>
+        <v>-0.912102604060306</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.966130450940252</v>
+        <v>-0.935397983455574</v>
       </c>
       <c r="C2" t="n">
-        <v>1.57879757108896</v>
+        <v>1.06083617103306</v>
       </c>
       <c r="D2" t="n">
-        <v>1.25442352351703</v>
+        <v>0.693621755344635</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.1011985555448</v>
+        <v>-1.0259239413049</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.1111167934351</v>
+        <v>-1.52301265969757</v>
       </c>
       <c r="G2" t="n">
-        <v>2.09398506157948</v>
+        <v>2.00310478458831</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-1.06667537541941</v>
+        <v>-1.06037910143119</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.977860558953474</v>
+        <v>-0.973314617748729</v>
       </c>
       <c r="C3" t="n">
-        <v>1.60270988921499</v>
+        <v>1.06081212090131</v>
       </c>
       <c r="D3" t="n">
-        <v>1.01401991995008</v>
+        <v>1.20126153786231</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.657840388449027</v>
+        <v>-0.917954358743702</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.15584254796252</v>
+        <v>-1.50710576118001</v>
       </c>
       <c r="G3" t="n">
-        <v>2.02023865052266</v>
+        <v>2.04534075352254</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-1.1257320133099</v>
+        <v>-1.11516864296256</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.866485386125988</v>
+        <v>-0.914135843071993</v>
       </c>
       <c r="C4" t="n">
-        <v>1.39654508767176</v>
+        <v>0.864528706642769</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4637690163652</v>
+        <v>1.02335879747838</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.986878027317621</v>
+        <v>-0.710013552116428</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.41984149075833</v>
+        <v>-1.20011926294722</v>
       </c>
       <c r="G4" t="n">
-        <v>1.99700871114399</v>
+        <v>2.01383913457869</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0.973339463345259</v>
+        <v>-1.02721451625072</v>
       </c>
       <c r="B5" t="n">
-        <v>-1.06428846806403</v>
+        <v>-0.996800744542072</v>
       </c>
       <c r="C5" t="n">
-        <v>1.59865353204725</v>
+        <v>1.05802151095789</v>
       </c>
       <c r="D5" t="n">
-        <v>1.05710401315127</v>
+        <v>1.05788769987012</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.15497044423114</v>
+        <v>-0.881209616614794</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.48113307189454</v>
+        <v>-1.52960302443418</v>
       </c>
       <c r="G5" t="n">
-        <v>2.05416470751759</v>
+        <v>2.00426728427828</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-1.19270364452244</v>
+        <v>-1.05334905448925</v>
       </c>
       <c r="B6" t="n">
-        <v>-1.11522842894086</v>
+        <v>-1.02291278773012</v>
       </c>
       <c r="C6" t="n">
-        <v>1.61001231300443</v>
+        <v>1.15490051855937</v>
       </c>
       <c r="D6" t="n">
-        <v>1.71236212081321</v>
+        <v>0.941121004417399</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.813138207370363</v>
+        <v>-0.66927535825232</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.39768321340917</v>
+        <v>-1.35166753444993</v>
       </c>
       <c r="G6" t="n">
-        <v>1.99903919975832</v>
+        <v>1.97839650010049</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-1.04916996278709</v>
+        <v>-1.01259954210213</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.97640394336385</v>
+        <v>-1.00958905011932</v>
       </c>
       <c r="C7" t="n">
-        <v>1.50274275292102</v>
+        <v>1.02774001032549</v>
       </c>
       <c r="D7" t="n">
-        <v>1.17544431643155</v>
+        <v>0.778378517418085</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.704885809940808</v>
+        <v>-1.09572859937209</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.36335439378113</v>
+        <v>-2.0609404049798</v>
       </c>
       <c r="G7" t="n">
-        <v>1.98654686439122</v>
+        <v>2.03461474348558</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0.922935527713008</v>
+        <v>-0.88226140057741</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.992513321280563</v>
+        <v>-0.70655373576193</v>
       </c>
       <c r="C8" t="n">
-        <v>1.5396022193586</v>
+        <v>0.76348739968763</v>
       </c>
       <c r="D8" t="n">
-        <v>0.900380840142005</v>
+        <v>0.788461174494143</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.979654348955453</v>
+        <v>-1.18077950060791</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.56227561029173</v>
+        <v>-1.50894590683005</v>
       </c>
       <c r="G8" t="n">
-        <v>1.94787732623169</v>
+        <v>2.10059476516529</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-0.987901694011946</v>
+        <v>-1.0818265282701</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.986126592035088</v>
+        <v>-0.894462337603579</v>
       </c>
       <c r="C9" t="n">
-        <v>1.58680750781231</v>
+        <v>0.871587323033968</v>
       </c>
       <c r="D9" t="n">
-        <v>1.39348333229182</v>
+        <v>1.09780587390707</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.07476314291266</v>
+        <v>-0.936408033584788</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.61265970126556</v>
+        <v>-1.29412617377533</v>
       </c>
       <c r="G9" t="n">
-        <v>2.02591203466667</v>
+        <v>1.99980129458453</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-1.03922495053485</v>
+        <v>-1.09608516992984</v>
       </c>
       <c r="B10" t="n">
-        <v>-1.08730507922097</v>
+        <v>-0.925017800616236</v>
       </c>
       <c r="C10" t="n">
-        <v>1.5179304790257</v>
+        <v>1.00349153118572</v>
       </c>
       <c r="D10" t="n">
-        <v>1.36667424542061</v>
+        <v>1.19594719704786</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.09813747028674</v>
+        <v>-0.997282115979138</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.55732399022754</v>
+        <v>-1.35572582590377</v>
       </c>
       <c r="G10" t="n">
-        <v>1.97238211995146</v>
+        <v>2.05111281414473</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-1.09357548696755</v>
+        <v>-0.961877367556752</v>
       </c>
       <c r="B11" t="n">
-        <v>-1.02753135469334</v>
+        <v>-1.05077377390006</v>
       </c>
       <c r="C11" t="n">
-        <v>1.65326412901146</v>
+        <v>1.21997172892007</v>
       </c>
       <c r="D11" t="n">
-        <v>1.32947727585802</v>
+        <v>0.925312187538693</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.75488332949947</v>
+        <v>-0.910337093635741</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.35517168103796</v>
+        <v>-1.52747252482726</v>
       </c>
       <c r="G11" t="n">
-        <v>2.00199488597044</v>
+        <v>2.06907921817894</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-0.970619952979732</v>
+        <v>-0.933190022028152</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.973091377753124</v>
+        <v>-0.913488003602079</v>
       </c>
       <c r="C12" t="n">
-        <v>1.51243832232243</v>
+        <v>0.974573944614118</v>
       </c>
       <c r="D12" t="n">
-        <v>1.09885214188791</v>
+        <v>0.837176498376227</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8176539979661</v>
+        <v>-1.08462119614247</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4737160299805</v>
+        <v>-1.47245445940949</v>
       </c>
       <c r="G12" t="n">
-        <v>2.07433141900672</v>
+        <v>2.02370257223962</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-1.08942695760442</v>
+        <v>-1.15633400388255</v>
       </c>
       <c r="B13" t="n">
-        <v>-1.03851028486007</v>
+        <v>-1.30490014689931</v>
       </c>
       <c r="C13" t="n">
-        <v>1.5616128714518</v>
+        <v>1.40710287417972</v>
       </c>
       <c r="D13" t="n">
-        <v>1.41548444678769</v>
+        <v>1.04765564156295</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.65236385117202</v>
+        <v>-0.708642760326744</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.39855423691291</v>
+        <v>-1.21573203694193</v>
       </c>
       <c r="G13" t="n">
-        <v>2.02115843882124</v>
+        <v>2.01442275415288</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-0.841066412154378</v>
+        <v>-0.815170505980165</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.92900747027324</v>
+        <v>-0.902377810769734</v>
       </c>
       <c r="C14" t="n">
-        <v>1.44774195494668</v>
+        <v>0.850599848115769</v>
       </c>
       <c r="D14" t="n">
-        <v>0.770904425176893</v>
+        <v>0.545941891800418</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.05864405483291</v>
+        <v>-1.17216753666932</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.54523406941582</v>
+        <v>-1.61823957372039</v>
       </c>
       <c r="G14" t="n">
-        <v>2.00918772595805</v>
+        <v>2.00566835207959</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-0.950583724378973</v>
+        <v>-1.08856405604732</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.96558597556065</v>
+        <v>-1.06575725300763</v>
       </c>
       <c r="C15" t="n">
-        <v>1.35545347389002</v>
+        <v>1.1722239371445</v>
       </c>
       <c r="D15" t="n">
-        <v>1.19844002774917</v>
+        <v>0.869889421172781</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.906882498494056</v>
+        <v>-0.775333508916687</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.56222708705288</v>
+        <v>-1.16264347589586</v>
       </c>
       <c r="G15" t="n">
-        <v>1.99896667548122</v>
+        <v>1.99301387499767</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-1.19334073759928</v>
+        <v>-1.0733388834313</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.747182585384883</v>
+        <v>-1.06263654899035</v>
       </c>
       <c r="C16" t="n">
-        <v>1.20311261244812</v>
+        <v>1.05694806576319</v>
       </c>
       <c r="D16" t="n">
-        <v>1.43789876102146</v>
+        <v>1.11940446996399</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.687320059935184</v>
+        <v>-1.12276736161902</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.14200070593643</v>
+        <v>-1.41392854815548</v>
       </c>
       <c r="G16" t="n">
-        <v>2.12405570211885</v>
+        <v>1.97538647545424</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-0.887588195457837</v>
+        <v>-1.01343649074514</v>
       </c>
       <c r="B17" t="n">
-        <v>-1.11138800025945</v>
+        <v>-1.0066845681776</v>
       </c>
       <c r="C17" t="n">
-        <v>1.67577945575668</v>
+        <v>0.954698027843053</v>
       </c>
       <c r="D17" t="n">
-        <v>0.824960226320526</v>
+        <v>1.02896337647453</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.996047807032162</v>
+        <v>-1.02673305039855</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.52912101990849</v>
+        <v>-1.42560059403931</v>
       </c>
       <c r="G17" t="n">
-        <v>1.98535564840975</v>
+        <v>1.92212796696379</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-0.962329236259028</v>
+        <v>-0.864145165758546</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.992686532376474</v>
+        <v>-0.851960498574252</v>
       </c>
       <c r="C18" t="n">
-        <v>1.48409653990818</v>
+        <v>0.831109624786719</v>
       </c>
       <c r="D18" t="n">
-        <v>1.13405949995909</v>
+        <v>0.504895582419933</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.71260707386691</v>
+        <v>-0.927559094752867</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.48589486681266</v>
+        <v>-1.46858835077284</v>
       </c>
       <c r="G18" t="n">
-        <v>1.99333076711578</v>
+        <v>1.89807040103333</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-1.07720846088167</v>
+        <v>-1.17357443278573</v>
       </c>
       <c r="B19" t="n">
-        <v>-1.05516647987388</v>
+        <v>-0.983833034626633</v>
       </c>
       <c r="C19" t="n">
-        <v>1.63402164589085</v>
+        <v>0.931888063429465</v>
       </c>
       <c r="D19" t="n">
-        <v>1.30912038309718</v>
+        <v>1.23241241857994</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.00249788957719</v>
+        <v>-0.664823132928853</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.08231954367456</v>
+        <v>-1.25064975558641</v>
       </c>
       <c r="G19" t="n">
-        <v>1.94988973469366</v>
+        <v>1.96948122346357</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-1.01610146793643</v>
+        <v>-1.13660386139094</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.921109870335908</v>
+        <v>-0.914870951077097</v>
       </c>
       <c r="C20" t="n">
-        <v>1.48285305783357</v>
+        <v>1.04273655578508</v>
       </c>
       <c r="D20" t="n">
-        <v>1.25003679654146</v>
+        <v>1.35764570420544</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.02617999872408</v>
+        <v>-0.915802756813818</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.54477372969004</v>
+        <v>-1.29335953301386</v>
       </c>
       <c r="G20" t="n">
-        <v>1.97558654877171</v>
+        <v>2.04311810002738</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-0.989579802026624</v>
+        <v>-0.901065671872998</v>
       </c>
       <c r="B21" t="n">
-        <v>-1.02527869474123</v>
+        <v>-1.02974679326372</v>
       </c>
       <c r="C21" t="n">
-        <v>1.51442148918185</v>
+        <v>1.0574575151704</v>
       </c>
       <c r="D21" t="n">
-        <v>0.877932059821514</v>
+        <v>0.675409348300865</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.13923894080459</v>
+        <v>-1.09642911795382</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.059713470984</v>
+        <v>-1.52833935178554</v>
       </c>
       <c r="G21" t="n">
-        <v>1.98530362419155</v>
+        <v>2.07482060975203</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-0.89046469372691</v>
+        <v>-0.87314537042508</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.949387729271006</v>
+        <v>-0.9684168477322</v>
       </c>
       <c r="C22" t="n">
-        <v>1.47564237863324</v>
+        <v>0.989743728553816</v>
       </c>
       <c r="D22" t="n">
-        <v>0.915427036766824</v>
+        <v>0.832779737972143</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.15638175605907</v>
+        <v>-1.17647220345756</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.38037780408624</v>
+        <v>-1.62881634331756</v>
       </c>
       <c r="G22" t="n">
-        <v>2.03201499395211</v>
+        <v>2.00440763383401</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-1.2511314384801</v>
+        <v>-1.11632874776146</v>
       </c>
       <c r="B23" t="n">
-        <v>-1.16825104826652</v>
+        <v>-1.02227428909227</v>
       </c>
       <c r="C23" t="n">
-        <v>1.70729746848967</v>
+        <v>1.04123494088747</v>
       </c>
       <c r="D23" t="n">
-        <v>1.49367521826184</v>
+        <v>1.08821811297164</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.953358556768267</v>
+        <v>-0.874664630097357</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.95145015702607</v>
+        <v>-1.15694558815169</v>
       </c>
       <c r="G23" t="n">
-        <v>1.95858520751317</v>
+        <v>1.98414643733799</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-0.985547206842611</v>
+        <v>-0.90568084099291</v>
       </c>
       <c r="B24" t="n">
-        <v>-1.07812824510933</v>
+        <v>-1.08119577970915</v>
       </c>
       <c r="C24" t="n">
-        <v>1.52315377969334</v>
+        <v>1.21464430282457</v>
       </c>
       <c r="D24" t="n">
-        <v>1.19140492506976</v>
+        <v>0.792352514412334</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.057686424173</v>
+        <v>-0.921459423068596</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.45139132118028</v>
+        <v>-1.57830500064856</v>
       </c>
       <c r="G24" t="n">
-        <v>2.03161655964332</v>
+        <v>1.91636336484501</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>-1.21894161121629</v>
+        <v>-1.18926047781941</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.931968652351965</v>
+        <v>-0.810392985810023</v>
       </c>
       <c r="C25" t="n">
-        <v>1.52782004029785</v>
+        <v>0.851385116849988</v>
       </c>
       <c r="D25" t="n">
-        <v>1.3667159306012</v>
+        <v>1.08076115038007</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.783833683785915</v>
+        <v>-0.762058528171795</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.78122533893158</v>
+        <v>-1.18945426159718</v>
       </c>
       <c r="G25" t="n">
-        <v>2.04316028589195</v>
+        <v>1.93991033907715</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-1.17313240432891</v>
+        <v>-1.17800994708412</v>
       </c>
       <c r="B26" t="n">
-        <v>-1.08232067657991</v>
+        <v>-1.06474566901107</v>
       </c>
       <c r="C26" t="n">
-        <v>1.57101613815039</v>
+        <v>1.06892809415424</v>
       </c>
       <c r="D26" t="n">
-        <v>1.39151557664496</v>
+        <v>1.27020928141183</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.99961299940941</v>
+        <v>-0.708313298673857</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.18590047294399</v>
+        <v>-1.2832099322963</v>
       </c>
       <c r="G26" t="n">
-        <v>2.01587595498083</v>
+        <v>1.96428423586154</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-0.852496329787025</v>
+        <v>-0.765926582107235</v>
       </c>
       <c r="B27" t="n">
-        <v>-1.09964917739311</v>
+        <v>-0.99328844765719</v>
       </c>
       <c r="C27" t="n">
-        <v>1.49885358401236</v>
+        <v>1.04235272059384</v>
       </c>
       <c r="D27" t="n">
-        <v>1.01540418952293</v>
+        <v>0.636071106011522</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.10822222668626</v>
+        <v>-1.30501434095783</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.72932840241792</v>
+        <v>-1.77852878931092</v>
       </c>
       <c r="G27" t="n">
-        <v>1.96014615343815</v>
+        <v>2.00324382765859</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>-0.941358375239667</v>
+        <v>-0.863775925601933</v>
       </c>
       <c r="B28" t="n">
-        <v>-1.03260398234074</v>
+        <v>-0.951115273717935</v>
       </c>
       <c r="C28" t="n">
-        <v>1.68701568353325</v>
+        <v>1.03511750164161</v>
       </c>
       <c r="D28" t="n">
-        <v>0.985380397732189</v>
+        <v>0.752742407780652</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.922124559510076</v>
+        <v>-1.04422169175502</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.50119736446319</v>
+        <v>-1.60572760946832</v>
       </c>
       <c r="G28" t="n">
-        <v>2.04942327057415</v>
+        <v>1.99723298005087</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>-0.892660838021876</v>
+        <v>-1.19933172165757</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.944826991974458</v>
+        <v>-1.04978408755938</v>
       </c>
       <c r="C29" t="n">
-        <v>1.47131051995996</v>
+        <v>1.07542063908187</v>
       </c>
       <c r="D29" t="n">
-        <v>1.06008580839154</v>
+        <v>1.26700816837391</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.16556447424769</v>
+        <v>-0.798580053030133</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.741149308366</v>
+        <v>-1.1852338611523</v>
       </c>
       <c r="G29" t="n">
-        <v>1.99949364917144</v>
+        <v>1.99832496304614</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>-1.18579687746792</v>
+        <v>-0.761846538968204</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.916031059111168</v>
+        <v>-0.780727339387062</v>
       </c>
       <c r="C30" t="n">
-        <v>1.45823906961985</v>
+        <v>0.806914846667716</v>
       </c>
       <c r="D30" t="n">
-        <v>1.75096096378732</v>
+        <v>0.386014565284259</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.978185891455047</v>
+        <v>-1.24818611602981</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.4064387188364</v>
+        <v>-1.66947418365019</v>
       </c>
       <c r="G30" t="n">
-        <v>1.9475003780885</v>
+        <v>2.09716828430434</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>-0.942873568278643</v>
+        <v>-1.14666635646548</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.884561578272439</v>
+        <v>-0.882572443796003</v>
       </c>
       <c r="C31" t="n">
-        <v>1.25230632619158</v>
+        <v>0.838023409250618</v>
       </c>
       <c r="D31" t="n">
-        <v>1.11533447201016</v>
+        <v>1.27886434658137</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.05755922140634</v>
+        <v>-0.940235658843197</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.51402327378989</v>
+        <v>-1.29553162887857</v>
       </c>
       <c r="G31" t="n">
-        <v>2.05414972850525</v>
+        <v>1.96644018362705</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>-1.06182629074526</v>
+        <v>-0.839174188815318</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.967777766805576</v>
+        <v>-1.1586974117351</v>
       </c>
       <c r="C32" t="n">
-        <v>1.42216836037202</v>
+        <v>1.28472971123967</v>
       </c>
       <c r="D32" t="n">
-        <v>1.27205085030387</v>
+        <v>0.652818817078446</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.779457109173125</v>
+        <v>-1.41067419746084</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.38232391946739</v>
+        <v>-2.3977789270265</v>
       </c>
       <c r="G32" t="n">
-        <v>1.95425809467788</v>
+        <v>1.96122020961769</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>-0.988379165318458</v>
+        <v>-0.943241174560921</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.784818389274093</v>
+        <v>-1.26915204534938</v>
       </c>
       <c r="C33" t="n">
-        <v>1.48137514215383</v>
+        <v>1.15089867522372</v>
       </c>
       <c r="D33" t="n">
-        <v>1.09056477825675</v>
+        <v>0.857794119512207</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.988886021647301</v>
+        <v>-1.21504395633185</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.60450691136264</v>
+        <v>-1.63272579646085</v>
       </c>
       <c r="G33" t="n">
-        <v>1.99385482511163</v>
+        <v>1.85676075875835</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>-0.979418331367923</v>
+        <v>-1.28936349987695</v>
       </c>
       <c r="B34" t="n">
-        <v>-1.17639336156539</v>
+        <v>-0.935234915497183</v>
       </c>
       <c r="C34" t="n">
-        <v>1.62653850084967</v>
+        <v>1.01311900008101</v>
       </c>
       <c r="D34" t="n">
-        <v>0.823104558673947</v>
+        <v>1.55710674970826</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.758253845495156</v>
+        <v>-0.674030098552566</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.34891079808142</v>
+        <v>-1.16237875668262</v>
       </c>
       <c r="G34" t="n">
-        <v>1.97402120054926</v>
+        <v>2.04862913954938</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>-1.32295822590766</v>
+        <v>-0.924913117700343</v>
       </c>
       <c r="B35" t="n">
-        <v>-1.02924107575732</v>
+        <v>-1.05911915526693</v>
       </c>
       <c r="C35" t="n">
-        <v>1.68608716454056</v>
+        <v>1.12208443954734</v>
       </c>
       <c r="D35" t="n">
-        <v>1.72170003944975</v>
+        <v>0.579737373581337</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.817504689167506</v>
+        <v>-0.862350994316213</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.7887989289648</v>
+        <v>-1.41340749765113</v>
       </c>
       <c r="G35" t="n">
-        <v>2.02916459969026</v>
+        <v>2.0397088649471</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>-1.3128424463174</v>
+        <v>-1.04873717343329</v>
       </c>
       <c r="B36" t="n">
-        <v>-1.15514161127735</v>
+        <v>-0.867652459483005</v>
       </c>
       <c r="C36" t="n">
-        <v>1.9629920139656</v>
+        <v>0.9215402579717</v>
       </c>
       <c r="D36" t="n">
-        <v>1.63968582087785</v>
+        <v>0.95618742883004</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.848078835210248</v>
+        <v>-0.769059712739092</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.78003721826915</v>
+        <v>-1.31356640423694</v>
       </c>
       <c r="G36" t="n">
-        <v>2.03717784065774</v>
+        <v>2.00703204768148</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>-0.866480204834266</v>
+        <v>-1.19069326362466</v>
       </c>
       <c r="B37" t="n">
-        <v>-1.28465539130146</v>
+        <v>-0.875334371012946</v>
       </c>
       <c r="C37" t="n">
-        <v>1.78173758729583</v>
+        <v>0.960822249088085</v>
       </c>
       <c r="D37" t="n">
-        <v>0.677770274293877</v>
+        <v>1.29552631456325</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.10941488897133</v>
+        <v>-0.722236614569042</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.4671117551774</v>
+        <v>-1.27443891404868</v>
       </c>
       <c r="G37" t="n">
-        <v>1.92423471262291</v>
+        <v>2.07237304895738</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>-0.83014250869484</v>
+        <v>-0.967410050471799</v>
       </c>
       <c r="B38" t="n">
-        <v>-0.865790619242786</v>
+        <v>-1.00298267400228</v>
       </c>
       <c r="C38" t="n">
-        <v>1.41599459083096</v>
+        <v>1.12407930881076</v>
       </c>
       <c r="D38" t="n">
-        <v>0.775978072504179</v>
+        <v>0.846318435896325</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.15311653716538</v>
+        <v>-1.09796271328547</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.59736772979934</v>
+        <v>-1.46847679185941</v>
       </c>
       <c r="G38" t="n">
-        <v>2.03456341988798</v>
+        <v>2.06601579200872</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>-1.00322389107775</v>
+        <v>-1.07518585960098</v>
       </c>
       <c r="B39" t="n">
-        <v>-1.15292534290331</v>
+        <v>-0.95902353543662</v>
       </c>
       <c r="C39" t="n">
-        <v>1.79499503666657</v>
+        <v>1.0610044362238</v>
       </c>
       <c r="D39" t="n">
-        <v>1.1189471174775</v>
+        <v>1.13748127902121</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.896656851637727</v>
+        <v>-0.618144671227977</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.33969177975541</v>
+        <v>-1.31789682232268</v>
       </c>
       <c r="G39" t="n">
-        <v>1.99023333002884</v>
+        <v>2.08887617843117</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>-0.928564873444676</v>
+        <v>-0.654963704147468</v>
       </c>
       <c r="B40" t="n">
-        <v>-1.11214666914117</v>
+        <v>-0.935904984211229</v>
       </c>
       <c r="C40" t="n">
-        <v>1.53629804422076</v>
+        <v>0.766879143395636</v>
       </c>
       <c r="D40" t="n">
-        <v>1.09103177689529</v>
+        <v>0.326976788413176</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.24038036699182</v>
+        <v>-1.43963238309494</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.65217701255829</v>
+        <v>-1.76560073081057</v>
       </c>
       <c r="G40" t="n">
-        <v>1.94129729871144</v>
+        <v>1.95961445638318</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>-1.01479249827388</v>
+        <v>-0.988855398619978</v>
       </c>
       <c r="B41" t="n">
-        <v>-1.08889259698972</v>
+        <v>-0.917116861229724</v>
       </c>
       <c r="C41" t="n">
-        <v>1.66378554443308</v>
+        <v>1.04931020095137</v>
       </c>
       <c r="D41" t="n">
-        <v>1.07421066991162</v>
+        <v>0.820993674668471</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.20910085469982</v>
+        <v>-0.860449055030115</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.22469754632143</v>
+        <v>-1.44424908473365</v>
       </c>
       <c r="G41" t="n">
-        <v>1.94074228825698</v>
+        <v>2.00215736439176</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>-1.08992004141424</v>
+        <v>-1.24514241020815</v>
       </c>
       <c r="B42" t="n">
-        <v>-0.982563160403144</v>
+        <v>-1.10111128479452</v>
       </c>
       <c r="C42" t="n">
-        <v>1.58122867786986</v>
+        <v>1.1155065729579</v>
       </c>
       <c r="D42" t="n">
-        <v>1.26439091109887</v>
+        <v>1.28183224261102</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.820649645483262</v>
+        <v>-0.556048604471255</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.3256251907564</v>
+        <v>-1.03471501495565</v>
       </c>
       <c r="G42" t="n">
-        <v>2.00716382023588</v>
+        <v>2.02746989600196</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>-0.960145116965509</v>
+        <v>-1.0444054516917</v>
       </c>
       <c r="B43" t="n">
-        <v>-1.08037198693706</v>
+        <v>-1.00668269509603</v>
       </c>
       <c r="C43" t="n">
-        <v>1.52683808871865</v>
+        <v>1.02584751656739</v>
       </c>
       <c r="D43" t="n">
-        <v>1.21277137882609</v>
+        <v>1.07446160756878</v>
       </c>
       <c r="E43" t="n">
-        <v>-1.15352324762557</v>
+        <v>-0.791238076005407</v>
       </c>
       <c r="F43" t="n">
-        <v>-1.69871569696488</v>
+        <v>-1.42280007138679</v>
       </c>
       <c r="G43" t="n">
-        <v>1.94276863635162</v>
+        <v>1.92869533627761</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>-1.04532213877053</v>
+        <v>-1.05391807860665</v>
       </c>
       <c r="B44" t="n">
-        <v>-0.87750807354587</v>
+        <v>-1.05039866862387</v>
       </c>
       <c r="C44" t="n">
-        <v>1.41736531385895</v>
+        <v>1.13517888678823</v>
       </c>
       <c r="D44" t="n">
-        <v>1.17665931568228</v>
+        <v>1.15038639140848</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.896186430773973</v>
+        <v>-0.884449889630795</v>
       </c>
       <c r="F44" t="n">
-        <v>-1.37224625482418</v>
+        <v>-1.41924534082688</v>
       </c>
       <c r="G44" t="n">
-        <v>2.08143810475473</v>
+        <v>2.06364643549567</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>-1.21361675079722</v>
+        <v>-0.963522433987934</v>
       </c>
       <c r="B45" t="n">
-        <v>-0.822297918563922</v>
+        <v>-1.09522388818569</v>
       </c>
       <c r="C45" t="n">
-        <v>1.29629467278839</v>
+        <v>1.08895532805969</v>
       </c>
       <c r="D45" t="n">
-        <v>1.42701839640006</v>
+        <v>1.00125723617838</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.642427078818754</v>
+        <v>-1.1101275806706</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.14897682817423</v>
+        <v>-1.61908556533573</v>
       </c>
       <c r="G45" t="n">
-        <v>2.06779543708607</v>
+        <v>1.91928610879254</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>-0.924425137434119</v>
+        <v>-0.90428728067953</v>
       </c>
       <c r="B46" t="n">
-        <v>-0.942122374174474</v>
+        <v>-0.931135841392181</v>
       </c>
       <c r="C46" t="n">
-        <v>1.31807565967181</v>
+        <v>1.08831196889514</v>
       </c>
       <c r="D46" t="n">
-        <v>1.09602764352123</v>
+        <v>0.848402526593232</v>
       </c>
       <c r="E46" t="n">
-        <v>-1.02683270450578</v>
+        <v>-1.1621952592087</v>
       </c>
       <c r="F46" t="n">
-        <v>-1.58906341255921</v>
+        <v>-1.56116220359196</v>
       </c>
       <c r="G46" t="n">
-        <v>2.01171601804911</v>
+        <v>2.09635725343326</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>-0.854936427350386</v>
+        <v>-0.910412311529016</v>
       </c>
       <c r="B47" t="n">
-        <v>-1.13658079782415</v>
+        <v>-1.04934624207846</v>
       </c>
       <c r="C47" t="n">
-        <v>1.71648038392153</v>
+        <v>1.14913457706318</v>
       </c>
       <c r="D47" t="n">
-        <v>1.00885983888406</v>
+        <v>0.830087617955768</v>
       </c>
       <c r="E47" t="n">
-        <v>-1.41712326839396</v>
+        <v>-1.20260314523075</v>
       </c>
       <c r="F47" t="n">
-        <v>-2.2538325330293</v>
+        <v>-1.54637530058447</v>
       </c>
       <c r="G47" t="n">
-        <v>2.04736240393712</v>
+        <v>2.00538478009888</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>-0.908788134785666</v>
+        <v>-1.1790319393222</v>
       </c>
       <c r="B48" t="n">
-        <v>-1.04138461674563</v>
+        <v>-0.94014258701629</v>
       </c>
       <c r="C48" t="n">
-        <v>1.6156897495457</v>
+        <v>0.99985947876196</v>
       </c>
       <c r="D48" t="n">
-        <v>0.907346063970055</v>
+        <v>1.31320485083985</v>
       </c>
       <c r="E48" t="n">
-        <v>-1.02066972710974</v>
+        <v>-0.728262311967901</v>
       </c>
       <c r="F48" t="n">
-        <v>-1.5170648040021</v>
+        <v>-1.21336065468723</v>
       </c>
       <c r="G48" t="n">
-        <v>1.99868840113688</v>
+        <v>1.98882659234607</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>-1.13316977928914</v>
+        <v>-1.05964933414183</v>
       </c>
       <c r="B49" t="n">
-        <v>-0.866901837173997</v>
+        <v>-0.961596662092439</v>
       </c>
       <c r="C49" t="n">
-        <v>1.36930623419162</v>
+        <v>1.00064975981077</v>
       </c>
       <c r="D49" t="n">
-        <v>1.39380845827758</v>
+        <v>0.935844166746533</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.81489737607094</v>
+        <v>-0.932748437612227</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.3097813358303</v>
+        <v>-1.29098256299197</v>
       </c>
       <c r="G49" t="n">
-        <v>2.03221479600901</v>
+        <v>2.04425748648522</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>-1.09899535390342</v>
+        <v>-1.0673037633364</v>
       </c>
       <c r="B50" t="n">
-        <v>-1.0087476743169</v>
+        <v>-1.09034847001467</v>
       </c>
       <c r="C50" t="n">
-        <v>1.49041585157838</v>
+        <v>1.12542891352597</v>
       </c>
       <c r="D50" t="n">
-        <v>1.20926443869168</v>
+        <v>0.9702729931745</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.695961292295362</v>
+        <v>-0.967856408422804</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.2392402696491</v>
+        <v>-1.46502981057604</v>
       </c>
       <c r="G50" t="n">
-        <v>2.00526324449949</v>
+        <v>1.90425723758904</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>-0.948378309827161</v>
+        <v>-0.738072227883142</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.896721030737805</v>
+        <v>-0.910460757577089</v>
       </c>
       <c r="C51" t="n">
-        <v>1.56957154259915</v>
+        <v>1.03203796504507</v>
       </c>
       <c r="D51" t="n">
-        <v>1.08230984323658</v>
+        <v>0.597435410392522</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.15399697342195</v>
+        <v>-1.31347366547168</v>
       </c>
       <c r="F51" t="n">
-        <v>-2.20126415053798</v>
+        <v>-1.71603209265109</v>
       </c>
       <c r="G51" t="n">
-        <v>2.04389462814054</v>
+        <v>1.99474586855915</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>-0.810777374131944</v>
+        <v>-1.0930654292303</v>
       </c>
       <c r="B52" t="n">
-        <v>-1.14077268541462</v>
+        <v>-1.05426741258679</v>
       </c>
       <c r="C52" t="n">
-        <v>1.6955198321556</v>
+        <v>1.22217774266858</v>
       </c>
       <c r="D52" t="n">
-        <v>0.744461686548982</v>
+        <v>1.11769488064158</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.27713578920687</v>
+        <v>-0.729806605364244</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.73989287808569</v>
+        <v>-1.3614699209342</v>
       </c>
       <c r="G52" t="n">
-        <v>2.03886055454182</v>
+        <v>2.08444789438855</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>-0.966582816023726</v>
+        <v>-1.30727803017661</v>
       </c>
       <c r="B53" t="n">
-        <v>-0.917928943687559</v>
+        <v>-0.855083754275319</v>
       </c>
       <c r="C53" t="n">
-        <v>1.42710867234127</v>
+        <v>0.807938452013071</v>
       </c>
       <c r="D53" t="n">
-        <v>1.17966365461197</v>
+        <v>1.42377113084501</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.15291039221131</v>
+        <v>-0.685351977406353</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.58887706761453</v>
+        <v>-1.12470506793155</v>
       </c>
       <c r="G53" t="n">
-        <v>2.04500350421317</v>
+        <v>2.01897468589859</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>-0.887728844387779</v>
+        <v>-0.914724761086799</v>
       </c>
       <c r="B54" t="n">
-        <v>-0.962898005618169</v>
+        <v>-1.01908852894149</v>
       </c>
       <c r="C54" t="n">
-        <v>1.45483453064644</v>
+        <v>1.02274089220476</v>
       </c>
       <c r="D54" t="n">
-        <v>0.904226898732347</v>
+        <v>0.679739107566486</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.13098024736118</v>
+        <v>-1.22792315768598</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.63295283697691</v>
+        <v>-2.11956217320102</v>
       </c>
       <c r="G54" t="n">
-        <v>1.97341652222954</v>
+        <v>2.01238650701792</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>-1.00150243088646</v>
+        <v>-0.948565748667446</v>
       </c>
       <c r="B55" t="n">
-        <v>-0.93190192667932</v>
+        <v>-1.08211858203395</v>
       </c>
       <c r="C55" t="n">
-        <v>1.46341144808877</v>
+        <v>0.994915191863001</v>
       </c>
       <c r="D55" t="n">
-        <v>1.16653098746483</v>
+        <v>0.92112834787572</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.971982198818244</v>
+        <v>-1.03189823242933</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.46348841043729</v>
+        <v>-1.56209748986463</v>
       </c>
       <c r="G55" t="n">
-        <v>2.07049380064059</v>
+        <v>1.95218579311584</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>-1.26776278694955</v>
+        <v>-0.944398584949011</v>
       </c>
       <c r="B56" t="n">
-        <v>-1.16475643629325</v>
+        <v>-0.92720700847712</v>
       </c>
       <c r="C56" t="n">
-        <v>1.75689791216575</v>
+        <v>1.008638621703</v>
       </c>
       <c r="D56" t="n">
-        <v>1.47638299992607</v>
+        <v>0.818341084552795</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.801808074067059</v>
+        <v>-0.954557577656958</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.72693093550713</v>
+        <v>-1.52156690012848</v>
       </c>
       <c r="G56" t="n">
-        <v>2.04864994644685</v>
+        <v>1.9895646225912</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>-1.06230042062042</v>
+        <v>-0.794387948828457</v>
       </c>
       <c r="B57" t="n">
-        <v>-1.12355053357831</v>
+        <v>-0.92848659263541</v>
       </c>
       <c r="C57" t="n">
-        <v>1.68792391862906</v>
+        <v>0.955179978877301</v>
       </c>
       <c r="D57" t="n">
-        <v>1.25952574546126</v>
+        <v>0.503313484072122</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.800048047498668</v>
+        <v>-1.11503264699104</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.37774680493923</v>
+        <v>-1.56770090499815</v>
       </c>
       <c r="G57" t="n">
-        <v>1.93496159843466</v>
+        <v>2.06321176956737</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>-0.99971489871188</v>
+        <v>-0.852155340186309</v>
       </c>
       <c r="B58" t="n">
-        <v>-0.81213096920974</v>
+        <v>-0.906749634382171</v>
       </c>
       <c r="C58" t="n">
-        <v>1.42906010178995</v>
+        <v>1.06467449360008</v>
       </c>
       <c r="D58" t="n">
-        <v>1.24509125823135</v>
+        <v>0.626871407874127</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.19977019733166</v>
+        <v>-1.04740222391719</v>
       </c>
       <c r="F58" t="n">
-        <v>-2.24331469768536</v>
+        <v>-1.6038523083424</v>
       </c>
       <c r="G58" t="n">
-        <v>2.0699742174289</v>
+        <v>2.09264415259403</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>-1.14838604388807</v>
+        <v>-0.995995380433004</v>
       </c>
       <c r="B59" t="n">
-        <v>-0.869597098986351</v>
+        <v>-1.01253301628778</v>
       </c>
       <c r="C59" t="n">
-        <v>1.42521142983422</v>
+        <v>0.979628114704033</v>
       </c>
       <c r="D59" t="n">
-        <v>1.43639506738618</v>
+        <v>0.931637842193204</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.853417573213411</v>
+        <v>-1.01445188619113</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.25288431647127</v>
+        <v>-1.42864714773876</v>
       </c>
       <c r="G59" t="n">
-        <v>2.08756815661228</v>
+        <v>1.93884300260507</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>-0.969383715284321</v>
+        <v>-1.10842145225557</v>
       </c>
       <c r="B60" t="n">
-        <v>-1.12867915080695</v>
+        <v>-0.956373095563243</v>
       </c>
       <c r="C60" t="n">
-        <v>1.74954042452314</v>
+        <v>0.929542345339532</v>
       </c>
       <c r="D60" t="n">
-        <v>1.02498881524923</v>
+        <v>1.00980689802813</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.19095716385693</v>
+        <v>-0.555610375404068</v>
       </c>
       <c r="F60" t="n">
-        <v>-2.21352249853673</v>
+        <v>-1.2784533593864</v>
       </c>
       <c r="G60" t="n">
-        <v>2.01880131956464</v>
+        <v>2.05737410075692</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>-0.826348630867626</v>
+        <v>-0.926202947626792</v>
       </c>
       <c r="B61" t="n">
-        <v>-1.00434067257819</v>
+        <v>-0.852996931373756</v>
       </c>
       <c r="C61" t="n">
-        <v>1.60164316233776</v>
+        <v>0.783748883353451</v>
       </c>
       <c r="D61" t="n">
-        <v>1.05777428816866</v>
+        <v>0.816771710930973</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.24758061680274</v>
+        <v>-0.9262140494484</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.62334576457372</v>
+        <v>-1.5355617090297</v>
       </c>
       <c r="G61" t="n">
-        <v>2.11279612371225</v>
+        <v>1.93828802281586</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>-0.995014581255241</v>
+        <v>-0.822112970275627</v>
       </c>
       <c r="B62" t="n">
-        <v>-1.05626211764655</v>
+        <v>-0.752008503638691</v>
       </c>
       <c r="C62" t="n">
-        <v>1.58204555139088</v>
+        <v>0.831737849355677</v>
       </c>
       <c r="D62" t="n">
-        <v>1.25821095995657</v>
+        <v>0.486000089923626</v>
       </c>
       <c r="E62" t="n">
-        <v>-1.22344825615567</v>
+        <v>-0.999551362000482</v>
       </c>
       <c r="F62" t="n">
-        <v>-2.2422981318381</v>
+        <v>-1.54912354054219</v>
       </c>
       <c r="G62" t="n">
-        <v>1.97724512911904</v>
+        <v>2.08986884215091</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>-1.03587283656583</v>
+        <v>-1.00543506608273</v>
       </c>
       <c r="B63" t="n">
-        <v>-1.11129093126015</v>
+        <v>-1.05172793120372</v>
       </c>
       <c r="C63" t="n">
-        <v>1.73633868715967</v>
+        <v>1.17673859359446</v>
       </c>
       <c r="D63" t="n">
-        <v>1.04899437871056</v>
+        <v>0.770690892664895</v>
       </c>
       <c r="E63" t="n">
-        <v>-1.06938235163544</v>
+        <v>-0.744541052474797</v>
       </c>
       <c r="F63" t="n">
-        <v>-2.06165561974017</v>
+        <v>-1.38161203937652</v>
       </c>
       <c r="G63" t="n">
-        <v>2.02050384044274</v>
+        <v>1.92143974744385</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>-1.26859040430865</v>
+        <v>-0.971145195287436</v>
       </c>
       <c r="B64" t="n">
-        <v>-0.870340439965813</v>
+        <v>-0.958187954263625</v>
       </c>
       <c r="C64" t="n">
-        <v>1.35645117114995</v>
+        <v>0.939294043520041</v>
       </c>
       <c r="D64" t="n">
-        <v>1.64388357837927</v>
+        <v>0.893712696007852</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.41817486366406</v>
+        <v>-1.02896275000289</v>
       </c>
       <c r="F64" t="n">
-        <v>-1.13086181991684</v>
+        <v>-1.48797098785809</v>
       </c>
       <c r="G64" t="n">
-        <v>2.13292552014288</v>
+        <v>2.08258786183265</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>-1.46250187873421</v>
+        <v>-1.06696826888488</v>
       </c>
       <c r="B65" t="n">
-        <v>-1.03461307872539</v>
+        <v>-1.02277003935945</v>
       </c>
       <c r="C65" t="n">
-        <v>1.46091875326483</v>
+        <v>0.977031092113534</v>
       </c>
       <c r="D65" t="n">
-        <v>1.77472622683653</v>
+        <v>0.903384502408576</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.579446034771519</v>
+        <v>-0.843203172614901</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.62634150093623</v>
+        <v>-1.29675740679401</v>
       </c>
       <c r="G65" t="n">
-        <v>2.03631154271278</v>
+        <v>1.92581842307888</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>-1.06346684342171</v>
+        <v>-0.91791020330032</v>
       </c>
       <c r="B66" t="n">
-        <v>-0.992085444892737</v>
+        <v>-0.993020596259524</v>
       </c>
       <c r="C66" t="n">
-        <v>1.54565906938699</v>
+        <v>0.92031074145179</v>
       </c>
       <c r="D66" t="n">
-        <v>1.42039507294368</v>
+        <v>0.918095551716867</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.796977891796009</v>
+        <v>-1.16653636120543</v>
       </c>
       <c r="F66" t="n">
-        <v>-1.4887514572123</v>
+        <v>-1.57354140666564</v>
       </c>
       <c r="G66" t="n">
-        <v>2.02313294229064</v>
+        <v>2.02234590633657</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>-1.17417779802908</v>
+        <v>-1.08748212689786</v>
       </c>
       <c r="B67" t="n">
-        <v>-0.988568836793802</v>
+        <v>-1.08087005203065</v>
       </c>
       <c r="C67" t="n">
-        <v>1.57664679284568</v>
+        <v>1.07219095146029</v>
       </c>
       <c r="D67" t="n">
-        <v>1.4856044122697</v>
+        <v>1.11386689136557</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.837647909544721</v>
+        <v>-0.956598658409892</v>
       </c>
       <c r="F67" t="n">
-        <v>-1.40591384361707</v>
+        <v>-1.41879463178214</v>
       </c>
       <c r="G67" t="n">
-        <v>2.01498960223147</v>
+        <v>2.02248556953427</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>-0.924946507033936</v>
+        <v>-0.928900235933482</v>
       </c>
       <c r="B68" t="n">
-        <v>-0.928324596113442</v>
+        <v>-0.895436656885807</v>
       </c>
       <c r="C68" t="n">
-        <v>1.49505238551236</v>
+        <v>1.0135339758174</v>
       </c>
       <c r="D68" t="n">
-        <v>1.02598257185295</v>
+        <v>1.06287298929326</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.11359770662474</v>
+        <v>-0.99094966453436</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.59817892327001</v>
+        <v>-1.71079131355043</v>
       </c>
       <c r="G68" t="n">
-        <v>1.98515155072768</v>
+        <v>2.07037151151312</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>-1.16745375448507</v>
+        <v>-0.88330791174128</v>
       </c>
       <c r="B69" t="n">
-        <v>-1.10730066123949</v>
+        <v>-0.976909771007685</v>
       </c>
       <c r="C69" t="n">
-        <v>1.662589763842</v>
+        <v>0.90278295742302</v>
       </c>
       <c r="D69" t="n">
-        <v>1.40942778568945</v>
+        <v>0.665885632274458</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.664646113515108</v>
+        <v>-0.940445122222752</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.28876421667387</v>
+        <v>-1.51478616203576</v>
       </c>
       <c r="G69" t="n">
-        <v>2.01574121640619</v>
+        <v>1.97838896585142</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>-1.10090550769668</v>
+        <v>-1.00072311074121</v>
       </c>
       <c r="B70" t="n">
-        <v>-1.11340872764412</v>
+        <v>-0.849347849372483</v>
       </c>
       <c r="C70" t="n">
-        <v>1.67230620453564</v>
+        <v>0.821332190173785</v>
       </c>
       <c r="D70" t="n">
-        <v>1.08341182662666</v>
+        <v>0.947094556616321</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.968262708612531</v>
+        <v>-0.884467279240427</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.87746561150828</v>
+        <v>-1.41100751912245</v>
       </c>
       <c r="G70" t="n">
-        <v>1.98879168167682</v>
+        <v>1.96476846280404</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>-1.05082074692962</v>
+        <v>-1.0217547621381</v>
       </c>
       <c r="B71" t="n">
-        <v>-0.953989769233343</v>
+        <v>-1.00658579865387</v>
       </c>
       <c r="C71" t="n">
-        <v>1.41905727141401</v>
+        <v>1.00218446435291</v>
       </c>
       <c r="D71" t="n">
-        <v>1.28276731413284</v>
+        <v>1.14337335774374</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.716266263450061</v>
+        <v>-0.945606273664287</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.36215960599162</v>
+        <v>-1.44530519973088</v>
       </c>
       <c r="G71" t="n">
-        <v>2.0245556309379</v>
+        <v>2.05040946039161</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>-1.24473630829935</v>
+        <v>-1.14803560288573</v>
       </c>
       <c r="B72" t="n">
-        <v>-0.996465775971678</v>
+        <v>-0.960399177833776</v>
       </c>
       <c r="C72" t="n">
-        <v>1.50653242550089</v>
+        <v>1.11131415365885</v>
       </c>
       <c r="D72" t="n">
-        <v>1.57264696273816</v>
+        <v>1.21646051500651</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.660416419220729</v>
+        <v>-1.00382507532221</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.10388632489617</v>
+        <v>-2.14768441512292</v>
       </c>
       <c r="G72" t="n">
-        <v>2.05379021824148</v>
+        <v>2.04210859758518</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>-1.08392127521861</v>
+        <v>-1.07695493029018</v>
       </c>
       <c r="B73" t="n">
-        <v>-1.19037913219937</v>
+        <v>-1.19573330597625</v>
       </c>
       <c r="C73" t="n">
-        <v>1.6303998669069</v>
+        <v>1.28281952028292</v>
       </c>
       <c r="D73" t="n">
-        <v>1.3058174663102</v>
+        <v>1.23404153061325</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.890858266007835</v>
+        <v>-0.942205328829573</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.41065514750085</v>
+        <v>-1.43537435612162</v>
       </c>
       <c r="G73" t="n">
-        <v>1.96167051865376</v>
+        <v>1.92972725689642</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>-1.07934318003931</v>
+        <v>-1.06172225917719</v>
       </c>
       <c r="B74" t="n">
-        <v>-1.00351935676498</v>
+        <v>-1.10709534039721</v>
       </c>
       <c r="C74" t="n">
-        <v>1.55944321952144</v>
+        <v>1.24784135075803</v>
       </c>
       <c r="D74" t="n">
-        <v>1.39318536657711</v>
+        <v>1.02350619632964</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.833345834536723</v>
+        <v>-1.13539765470192</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.41729803106242</v>
+        <v>-2.15212732363856</v>
       </c>
       <c r="G74" t="n">
-        <v>1.98949237954102</v>
+        <v>2.02696425732154</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>-0.975845330009707</v>
+        <v>-0.973521861530144</v>
       </c>
       <c r="B75" t="n">
-        <v>-1.02301376507309</v>
+        <v>-0.942889098039707</v>
       </c>
       <c r="C75" t="n">
-        <v>1.47882966099145</v>
+        <v>0.974591071419667</v>
       </c>
       <c r="D75" t="n">
-        <v>1.17795784669144</v>
+        <v>0.897350706820523</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.905493924559639</v>
+        <v>-0.997839400874963</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.3769957672812</v>
+        <v>-1.37614196316336</v>
       </c>
       <c r="G75" t="n">
-        <v>1.98690607988499</v>
+        <v>2.00215376945834</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>-0.983311350982681</v>
+        <v>-0.993365378755465</v>
       </c>
       <c r="B76" t="n">
-        <v>-0.918657549605849</v>
+        <v>-0.911618703940826</v>
       </c>
       <c r="C76" t="n">
-        <v>1.5241659683195</v>
+        <v>0.899768165326941</v>
       </c>
       <c r="D76" t="n">
-        <v>1.19568059532462</v>
+        <v>1.02553142774413</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.747008845148916</v>
+        <v>-0.876147059790809</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.38939067415353</v>
+        <v>-1.44613439983232</v>
       </c>
       <c r="G76" t="n">
-        <v>2.10067820747716</v>
+        <v>2.0075052794833</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>-0.99698958870583</v>
+        <v>-0.823451191624121</v>
       </c>
       <c r="B77" t="n">
-        <v>-0.945953371635499</v>
+        <v>-0.925668348299375</v>
       </c>
       <c r="C77" t="n">
-        <v>1.42408823764982</v>
+        <v>1.0700862826573</v>
       </c>
       <c r="D77" t="n">
-        <v>1.03775890425266</v>
+        <v>0.482881039998684</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.856645193001229</v>
+        <v>-0.954137418266629</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.40348937054707</v>
+        <v>-1.59283506851853</v>
       </c>
       <c r="G77" t="n">
-        <v>2.04598648231122</v>
+        <v>1.9823212828993</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>-1.05868746790948</v>
+        <v>-0.977432204339522</v>
       </c>
       <c r="B78" t="n">
-        <v>-1.20312064707079</v>
+        <v>-0.998309533310954</v>
       </c>
       <c r="C78" t="n">
-        <v>1.72866955633128</v>
+        <v>1.02676539148096</v>
       </c>
       <c r="D78" t="n">
-        <v>1.22682438787792</v>
+        <v>0.94216750644868</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.830304392531043</v>
+        <v>-1.06772595586057</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.39491633662054</v>
+        <v>-1.51694979100183</v>
       </c>
       <c r="G78" t="n">
-        <v>1.96527862496048</v>
+        <v>2.01660018925476</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>-1.20389038452557</v>
+        <v>-0.975940946170272</v>
       </c>
       <c r="B79" t="n">
-        <v>-1.01881342808289</v>
+        <v>-0.905021134173246</v>
       </c>
       <c r="C79" t="n">
-        <v>1.48168547965604</v>
+        <v>0.992134217539239</v>
       </c>
       <c r="D79" t="n">
-        <v>1.68275745002592</v>
+        <v>0.58928642363987</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.928059153100779</v>
+        <v>-0.839038311373515</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.35956070209949</v>
+        <v>-1.28612325845282</v>
       </c>
       <c r="G79" t="n">
-        <v>1.98766603725574</v>
+        <v>2.07726986971642</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>-1.13891442050358</v>
+        <v>-1.07928294799849</v>
       </c>
       <c r="B80" t="n">
-        <v>-1.2207383504726</v>
+        <v>-1.15035529307872</v>
       </c>
       <c r="C80" t="n">
-        <v>1.76231505205074</v>
+        <v>1.12710408460607</v>
       </c>
       <c r="D80" t="n">
-        <v>1.25815574023558</v>
+        <v>0.99297008860025</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.988068577363604</v>
+        <v>-0.915054420354323</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.85481338256996</v>
+        <v>-1.32497753139865</v>
       </c>
       <c r="G80" t="n">
-        <v>1.98965263329264</v>
+        <v>1.93402233740289</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>-0.851384829480597</v>
+        <v>-0.826349563274627</v>
       </c>
       <c r="B81" t="n">
-        <v>-1.06024876577785</v>
+        <v>-0.97428958560875</v>
       </c>
       <c r="C81" t="n">
-        <v>1.6162701736861</v>
+        <v>0.960067258955508</v>
       </c>
       <c r="D81" t="n">
-        <v>0.689676739166483</v>
+        <v>0.781308156758805</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.924500521948603</v>
+        <v>-1.29724084121817</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.55071704321632</v>
+        <v>-1.68775538225233</v>
       </c>
       <c r="G81" t="n">
-        <v>2.06841949624755</v>
+        <v>2.02904630412801</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>-0.987174452152025</v>
+        <v>-0.906145586454433</v>
       </c>
       <c r="B82" t="n">
-        <v>-1.07225315056898</v>
+        <v>-0.970095528207345</v>
       </c>
       <c r="C82" t="n">
-        <v>1.65607732879132</v>
+        <v>1.07100967577909</v>
       </c>
       <c r="D82" t="n">
-        <v>1.14204990109799</v>
+        <v>0.81930956617951</v>
       </c>
       <c r="E82" t="n">
-        <v>-1.06344239950891</v>
+        <v>-1.1724628356437</v>
       </c>
       <c r="F82" t="n">
-        <v>-1.51407328872648</v>
+        <v>-1.51535956914417</v>
       </c>
       <c r="G82" t="n">
-        <v>2.05388901403986</v>
+        <v>2.05602464304913</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>-0.982592897264841</v>
+        <v>-1.2106054552776</v>
       </c>
       <c r="B83" t="n">
-        <v>-1.1231937788693</v>
+        <v>-1.08913643521853</v>
       </c>
       <c r="C83" t="n">
-        <v>1.69465268255444</v>
+        <v>1.05809195698244</v>
       </c>
       <c r="D83" t="n">
-        <v>1.10154678885314</v>
+        <v>1.57203665049676</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.874969096422426</v>
+        <v>-1.00734146258042</v>
       </c>
       <c r="F83" t="n">
-        <v>-1.40492186953215</v>
+        <v>-1.29914550433705</v>
       </c>
       <c r="G83" t="n">
-        <v>2.02494731756419</v>
+        <v>1.97649866892124</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>-1.04759261262373</v>
+        <v>-1.14520930281326</v>
       </c>
       <c r="B84" t="n">
-        <v>-1.00739414651418</v>
+        <v>-1.11108341030598</v>
       </c>
       <c r="C84" t="n">
-        <v>1.4271721069804</v>
+        <v>1.1207525991582</v>
       </c>
       <c r="D84" t="n">
-        <v>1.35311676318658</v>
+        <v>1.02808246990725</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.788985369654664</v>
+        <v>-1.00044027703724</v>
       </c>
       <c r="F84" t="n">
-        <v>-1.4189498251474</v>
+        <v>-2.00316664227171</v>
       </c>
       <c r="G84" t="n">
-        <v>1.94707353101995</v>
+        <v>1.93117513578709</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>-1.19048539780555</v>
+        <v>-0.830825269441087</v>
       </c>
       <c r="B85" t="n">
-        <v>-0.93392433389886</v>
+        <v>-0.92647294749361</v>
       </c>
       <c r="C85" t="n">
-        <v>1.38805948461536</v>
+        <v>0.979598446709049</v>
       </c>
       <c r="D85" t="n">
-        <v>1.60752666850456</v>
+        <v>0.761038347946728</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.613573854672899</v>
+        <v>-1.05962368693331</v>
       </c>
       <c r="F85" t="n">
-        <v>-1.32742813139162</v>
+        <v>-1.62434245796715</v>
       </c>
       <c r="G85" t="n">
-        <v>1.97831697160047</v>
+        <v>2.06566481792158</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>-1.15430837020707</v>
+        <v>-0.79313168681784</v>
       </c>
       <c r="B86" t="n">
-        <v>-1.13733370936033</v>
+        <v>-1.04567721003919</v>
       </c>
       <c r="C86" t="n">
-        <v>1.79590356223535</v>
+        <v>0.923421902669937</v>
       </c>
       <c r="D86" t="n">
-        <v>1.37087149250895</v>
+        <v>0.606820143090163</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.870365701923991</v>
+        <v>-1.03143050758926</v>
       </c>
       <c r="F86" t="n">
-        <v>-1.2383302049741</v>
+        <v>-1.65925626275556</v>
       </c>
       <c r="G86" t="n">
-        <v>1.99271972774127</v>
+        <v>2.05533609133388</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>-0.972214903767455</v>
+        <v>-1.0076737143176</v>
       </c>
       <c r="B87" t="n">
-        <v>-0.892407881184301</v>
+        <v>-0.853935140653942</v>
       </c>
       <c r="C87" t="n">
-        <v>1.34954220082508</v>
+        <v>0.99434445722942</v>
       </c>
       <c r="D87" t="n">
-        <v>0.852224154074395</v>
+        <v>0.923474413058156</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.735210756184804</v>
+        <v>-0.798695943554337</v>
       </c>
       <c r="F87" t="n">
-        <v>-1.17067092078938</v>
+        <v>-1.46355505704307</v>
       </c>
       <c r="G87" t="n">
-        <v>2.09800215820061</v>
+        <v>1.99046595091423</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>-0.950903455200498</v>
+        <v>-1.09387682041683</v>
       </c>
       <c r="B88" t="n">
-        <v>-1.0401439925986</v>
+        <v>-0.983560383961404</v>
       </c>
       <c r="C88" t="n">
-        <v>1.42183972701422</v>
+        <v>1.09312074963739</v>
       </c>
       <c r="D88" t="n">
-        <v>1.14830275359495</v>
+        <v>1.20497022965816</v>
       </c>
       <c r="E88" t="n">
-        <v>-1.11517340888891</v>
+        <v>-0.721152368274054</v>
       </c>
       <c r="F88" t="n">
-        <v>-1.56246860705405</v>
+        <v>-1.39794665785957</v>
       </c>
       <c r="G88" t="n">
-        <v>2.01815747145556</v>
+        <v>1.94065424722634</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>-1.153557708572</v>
+        <v>-0.91582083585181</v>
       </c>
       <c r="B89" t="n">
-        <v>-1.06634662218535</v>
+        <v>-1.20924906107144</v>
       </c>
       <c r="C89" t="n">
-        <v>1.46466023550354</v>
+        <v>1.32702368324093</v>
       </c>
       <c r="D89" t="n">
-        <v>1.52857622722487</v>
+        <v>0.681611924991864</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.686882553418076</v>
+        <v>-1.09931400577001</v>
       </c>
       <c r="F89" t="n">
-        <v>-1.28087281947952</v>
+        <v>-1.4260814588149</v>
       </c>
       <c r="G89" t="n">
-        <v>1.98747468239083</v>
+        <v>1.89907949250715</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>-0.950689409043596</v>
+        <v>-1.11726009630544</v>
       </c>
       <c r="B90" t="n">
-        <v>-1.15794786502201</v>
+        <v>-0.91923457777606</v>
       </c>
       <c r="C90" t="n">
-        <v>1.81972858008629</v>
+        <v>0.835978434075732</v>
       </c>
       <c r="D90" t="n">
-        <v>0.814464680843162</v>
+        <v>1.08841241454264</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.903377882149297</v>
+        <v>-0.761170121805207</v>
       </c>
       <c r="F90" t="n">
-        <v>-1.42563049639642</v>
+        <v>-1.26674434521983</v>
       </c>
       <c r="G90" t="n">
-        <v>1.99043950674464</v>
+        <v>1.9766985563077</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>-0.988428077557848</v>
+        <v>-1.07393973081185</v>
       </c>
       <c r="B91" t="n">
-        <v>-0.794192497484284</v>
+        <v>-0.981200993773635</v>
       </c>
       <c r="C91" t="n">
-        <v>1.2966835845714</v>
+        <v>1.00187265427708</v>
       </c>
       <c r="D91" t="n">
-        <v>1.11856218068759</v>
+        <v>1.03613632312981</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.980036358194545</v>
+        <v>-0.986913008981532</v>
       </c>
       <c r="F91" t="n">
-        <v>-1.44128732182317</v>
+        <v>-1.35675182036146</v>
       </c>
       <c r="G91" t="n">
-        <v>2.10578141191555</v>
+        <v>1.99468833129809</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>-0.9289780873553</v>
+        <v>-1.11035341226156</v>
       </c>
       <c r="B92" t="n">
-        <v>-1.08499152048837</v>
+        <v>-1.04066090175035</v>
       </c>
       <c r="C92" t="n">
-        <v>1.5641702798502</v>
+        <v>1.01534194523645</v>
       </c>
       <c r="D92" t="n">
-        <v>0.955247012127195</v>
+        <v>1.15288569399184</v>
       </c>
       <c r="E92" t="n">
-        <v>-1.27294984475444</v>
+        <v>-0.809458970230825</v>
       </c>
       <c r="F92" t="n">
-        <v>-2.2657840823476</v>
+        <v>-1.33393334821512</v>
       </c>
       <c r="G92" t="n">
-        <v>1.89485038305992</v>
+        <v>1.99517572385954</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>-1.10569141925705</v>
+        <v>-1.2149227940792</v>
       </c>
       <c r="B93" t="n">
-        <v>-1.11826596086212</v>
+        <v>-1.08873475071534</v>
       </c>
       <c r="C93" t="n">
-        <v>1.6612504651196</v>
+        <v>1.06910722410165</v>
       </c>
       <c r="D93" t="n">
-        <v>1.39187923810946</v>
+        <v>1.20944390670522</v>
       </c>
       <c r="E93" t="n">
-        <v>-1.07631495489773</v>
+        <v>-0.762881173403434</v>
       </c>
       <c r="F93" t="n">
-        <v>-2.27868986951652</v>
+        <v>-1.10359516905547</v>
       </c>
       <c r="G93" t="n">
-        <v>1.97641190309396</v>
+        <v>1.96851019797388</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>-1.05139558565127</v>
+        <v>-1.17275370330743</v>
       </c>
       <c r="B94" t="n">
-        <v>-1.22347760054178</v>
+        <v>-1.01849869173672</v>
       </c>
       <c r="C94" t="n">
-        <v>1.72072289255833</v>
+        <v>1.15673891224623</v>
       </c>
       <c r="D94" t="n">
-        <v>0.962757755037039</v>
+        <v>1.24209489047042</v>
       </c>
       <c r="E94" t="n">
-        <v>-1.07775157776413</v>
+        <v>-0.780588330884482</v>
       </c>
       <c r="F94" t="n">
-        <v>-2.07280287906507</v>
+        <v>-1.28973672634774</v>
       </c>
       <c r="G94" t="n">
-        <v>1.86476174465625</v>
+        <v>1.97866485533622</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>-0.989969866712943</v>
+        <v>-0.940179258274485</v>
       </c>
       <c r="B95" t="n">
-        <v>-0.97636849888413</v>
+        <v>-0.891344766014926</v>
       </c>
       <c r="C95" t="n">
-        <v>1.38196711766796</v>
+        <v>1.01639287560106</v>
       </c>
       <c r="D95" t="n">
-        <v>1.08206276805982</v>
+        <v>0.837533525819723</v>
       </c>
       <c r="E95" t="n">
-        <v>-1.26241273365475</v>
+        <v>-0.974399921559473</v>
       </c>
       <c r="F95" t="n">
-        <v>-2.39437187748784</v>
+        <v>-1.52676504969851</v>
       </c>
       <c r="G95" t="n">
-        <v>2.00856710785518</v>
+        <v>1.97660908691258</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>-1.19765384755402</v>
+        <v>-1.23704026314492</v>
       </c>
       <c r="B96" t="n">
-        <v>-1.17621662490539</v>
+        <v>-0.878082641431707</v>
       </c>
       <c r="C96" t="n">
-        <v>1.74457241167247</v>
+        <v>0.804284765048698</v>
       </c>
       <c r="D96" t="n">
-        <v>1.34626689606902</v>
+        <v>1.42371764515421</v>
       </c>
       <c r="E96" t="n">
-        <v>-1.01299459543574</v>
+        <v>-0.991440541419864</v>
       </c>
       <c r="F96" t="n">
-        <v>-1.86607010521696</v>
+        <v>-1.21850514466292</v>
       </c>
       <c r="G96" t="n">
-        <v>1.97697050567543</v>
+        <v>1.99324809726635</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>-0.862733071785238</v>
+        <v>-1.12834899984271</v>
       </c>
       <c r="B97" t="n">
-        <v>-0.980693610994576</v>
+        <v>-1.04738844630922</v>
       </c>
       <c r="C97" t="n">
-        <v>1.42125178676872</v>
+        <v>0.980648702445102</v>
       </c>
       <c r="D97" t="n">
-        <v>0.870947851193553</v>
+        <v>1.05643472615044</v>
       </c>
       <c r="E97" t="n">
-        <v>-1.09567478047953</v>
+        <v>-0.741795954465729</v>
       </c>
       <c r="F97" t="n">
-        <v>-1.59848924349239</v>
+        <v>-1.34069281443861</v>
       </c>
       <c r="G97" t="n">
-        <v>1.96984320096315</v>
+        <v>1.95562272410962</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>-1.0230258106123</v>
+        <v>-1.23209390093788</v>
       </c>
       <c r="B98" t="n">
-        <v>-1.25819301697263</v>
+        <v>-0.914228870307251</v>
       </c>
       <c r="C98" t="n">
-        <v>1.75693206450492</v>
+        <v>0.967128121466894</v>
       </c>
       <c r="D98" t="n">
-        <v>1.0201042381361</v>
+        <v>1.34336202613363</v>
       </c>
       <c r="E98" t="n">
-        <v>-1.12247015766043</v>
+        <v>-0.612109285982388</v>
       </c>
       <c r="F98" t="n">
-        <v>-2.14771181074248</v>
+        <v>-1.20076097704881</v>
       </c>
       <c r="G98" t="n">
-        <v>2.05062711908696</v>
+        <v>2.01926404873706</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>-0.926401282928886</v>
+        <v>-1.1902148557791</v>
       </c>
       <c r="B99" t="n">
-        <v>-0.986506122826108</v>
+        <v>-1.16783967016411</v>
       </c>
       <c r="C99" t="n">
-        <v>1.57198568480085</v>
+        <v>1.09406333773333</v>
       </c>
       <c r="D99" t="n">
-        <v>0.962086477392435</v>
+        <v>1.32119509641252</v>
       </c>
       <c r="E99" t="n">
-        <v>-1.09521598123892</v>
+        <v>-0.566184489166273</v>
       </c>
       <c r="F99" t="n">
-        <v>-1.59161112759159</v>
+        <v>-1.26840253617746</v>
       </c>
       <c r="G99" t="n">
-        <v>2.00137227328857</v>
+        <v>1.96249765448034</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>-1.02611960994552</v>
+        <v>-1.02993668046582</v>
       </c>
       <c r="B100" t="n">
-        <v>-1.07028856086338</v>
+        <v>-0.81265615581669</v>
       </c>
       <c r="C100" t="n">
-        <v>1.51077725370412</v>
+        <v>0.783202431790196</v>
       </c>
       <c r="D100" t="n">
-        <v>1.28203271439634</v>
+        <v>0.736264293582432</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.840547005879873</v>
+        <v>-0.723619391372555</v>
       </c>
       <c r="F100" t="n">
-        <v>-1.41970267444138</v>
+        <v>-1.27144824480731</v>
       </c>
       <c r="G100" t="n">
-        <v>2.03946112287967</v>
+        <v>2.07187070207258</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>-1.2339821862671</v>
+        <v>-1.07432236631312</v>
       </c>
       <c r="B101" t="n">
-        <v>-0.992336601713076</v>
+        <v>-0.904493148561047</v>
       </c>
       <c r="C101" t="n">
-        <v>1.55078208857155</v>
+        <v>1.04521581733852</v>
       </c>
       <c r="D101" t="n">
-        <v>1.4079441918506</v>
+        <v>1.20500537755071</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.542715624458228</v>
+        <v>-0.825408112830527</v>
       </c>
       <c r="F101" t="n">
-        <v>-1.18147299208136</v>
+        <v>-1.37241396564134</v>
       </c>
       <c r="G101" t="n">
-        <v>2.01724791505933</v>
+        <v>2.00001365968414</v>
       </c>
     </row>
   </sheetData>
@@ -3149,826 +3152,826 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.102948838780457</v>
+        <v>2.73809462689463</v>
       </c>
       <c r="B2" t="n">
-        <v>0.307516098344397</v>
+        <v>0.252823322449368</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.123087446828943</v>
+        <v>1.8868272039055</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0895748503095675</v>
+        <v>0.24343272570746</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.76993286218773</v>
+        <v>0.0487583585600892</v>
       </c>
       <c r="B4" t="n">
-        <v>0.177248156654464</v>
+        <v>0.029730998349411</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.709258561743168</v>
+        <v>2.37470352351904</v>
       </c>
       <c r="B5" t="n">
-        <v>0.228369753795137</v>
+        <v>0.260232489299897</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.313807306411416</v>
+        <v>0.48914113182906</v>
       </c>
       <c r="B6" t="n">
-        <v>0.163318796482445</v>
+        <v>0.123195142627054</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.674543717640085</v>
+        <v>0.112529794426252</v>
       </c>
       <c r="B7" t="n">
-        <v>0.132362393144313</v>
+        <v>0.295353622274137</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3.93908875641319</v>
+        <v>2.90690964183589</v>
       </c>
       <c r="B8" t="n">
-        <v>0.283007578790895</v>
+        <v>0.247652784743946</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5.20137621509663</v>
+        <v>0.129675151668163</v>
       </c>
       <c r="B9" t="n">
-        <v>0.316489218204826</v>
+        <v>0.0810382647785097</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2.63262155782951</v>
+        <v>0.367831902332545</v>
       </c>
       <c r="B10" t="n">
-        <v>0.282382405988231</v>
+        <v>0.129554178018723</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.268662048968746</v>
+        <v>2.53036202941922</v>
       </c>
       <c r="B11" t="n">
-        <v>0.131399124034076</v>
+        <v>0.257873336281972</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1.81769541771037</v>
+        <v>1.83758185383185</v>
       </c>
       <c r="B12" t="n">
-        <v>0.214161803055934</v>
+        <v>0.223066332647942</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.601199728799515</v>
+        <v>0.0834671683778235</v>
       </c>
       <c r="B13" t="n">
-        <v>0.160323954603226</v>
+        <v>0.0339808798446795</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3.58859348498451</v>
+        <v>6.28448133246812</v>
       </c>
       <c r="B14" t="n">
-        <v>0.26945693108031</v>
+        <v>0.329302119705438</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3.93044965996941</v>
+        <v>0.137422312631723</v>
       </c>
       <c r="B15" t="n">
-        <v>0.292152673919692</v>
+        <v>0.0870535021140463</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.143237443452989</v>
+        <v>0.708068103507569</v>
       </c>
       <c r="B16" t="n">
-        <v>0.110128801531856</v>
+        <v>0.174951418116259</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2.89421181286444</v>
+        <v>0.902803610627275</v>
       </c>
       <c r="B17" t="n">
-        <v>0.261449539442802</v>
+        <v>0.184495704344305</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2.58580422007508</v>
+        <v>2.15261981296706</v>
       </c>
       <c r="B18" t="n">
-        <v>0.230027817869879</v>
+        <v>0.216851408362502</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.184269107893657</v>
+        <v>0.0583616333461877</v>
       </c>
       <c r="B19" t="n">
-        <v>0.307712046852136</v>
+        <v>0.0493039635967559</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2.48148209933794</v>
+        <v>0.0930743798327848</v>
       </c>
       <c r="B20" t="n">
-        <v>0.266333763899049</v>
+        <v>0.0793719960376971</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.113042035875016</v>
+        <v>1.43793011427901</v>
       </c>
       <c r="B21" t="n">
-        <v>0.279346280931699</v>
+        <v>0.276412974322523</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1.03968442244442</v>
+        <v>8.52943157431596</v>
       </c>
       <c r="B22" t="n">
-        <v>0.407519190948897</v>
+        <v>0.337489363333274</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.130887069975538</v>
+        <v>0.181361497819796</v>
       </c>
       <c r="B23" t="n">
-        <v>0.267045422004263</v>
+        <v>0.0991561624206528</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1.44849953503276</v>
+        <v>4.64540560183797</v>
       </c>
       <c r="B24" t="n">
-        <v>0.195959060888884</v>
+        <v>0.289286536802111</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.125065464164237</v>
+        <v>0.106267769286555</v>
       </c>
       <c r="B25" t="n">
-        <v>0.257064304000023</v>
+        <v>0.0610379905727562</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.124410438078719</v>
+        <v>0.110161162680962</v>
       </c>
       <c r="B26" t="n">
-        <v>0.31749310623906</v>
+        <v>0.0691995345827435</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>12.3819104618846</v>
+        <v>32.974998827</v>
       </c>
       <c r="B27" t="n">
-        <v>0.396980986616702</v>
+        <v>0.420685884585408</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1.69649855579668</v>
+        <v>5.75154492691927</v>
       </c>
       <c r="B28" t="n">
-        <v>0.233545382634106</v>
+        <v>0.316440422682623</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>14.0383127259723</v>
+        <v>0.0738248065113006</v>
       </c>
       <c r="B29" t="n">
-        <v>0.401497105320519</v>
+        <v>0.0469522691322813</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.626089583993891</v>
+        <v>10.6891795957254</v>
       </c>
       <c r="B30" t="n">
-        <v>0.172486251979717</v>
+        <v>0.354303200315525</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2.36567471936266</v>
+        <v>0.13467457181593</v>
       </c>
       <c r="B31" t="n">
-        <v>0.245113557367219</v>
+        <v>0.0848973350177175</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.564428712345561</v>
+        <v>3.18928640896498</v>
       </c>
       <c r="B32" t="n">
-        <v>0.147401269750792</v>
+        <v>0.420073427844262</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3.79935128712093</v>
+        <v>4.33045190905714</v>
       </c>
       <c r="B33" t="n">
-        <v>0.314586156355984</v>
+        <v>0.345862501284622</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.290905507495145</v>
+        <v>0.210921377142069</v>
       </c>
       <c r="B34" t="n">
-        <v>0.124751614972763</v>
+        <v>0.109358657193625</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.234388069294676</v>
+        <v>0.944900688767505</v>
       </c>
       <c r="B35" t="n">
-        <v>0.222982319965756</v>
+        <v>0.179642271307711</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.166434343418285</v>
+        <v>0.201800645656881</v>
       </c>
       <c r="B36" t="n">
-        <v>0.215934885378039</v>
+        <v>0.094575501341623</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1.41052168215051</v>
+        <v>0.0553162206115388</v>
       </c>
       <c r="B37" t="n">
-        <v>0.223659102723893</v>
+        <v>0.0606006369694178</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>4.75592413145574</v>
+        <v>1.74288384635595</v>
       </c>
       <c r="B38" t="n">
-        <v>0.318033670824403</v>
+        <v>0.221509354560828</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.21523129626277</v>
+        <v>0.0952526191854981</v>
       </c>
       <c r="B39" t="n">
-        <v>0.11698196848313</v>
+        <v>0.102044823519025</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>7.7753862037977</v>
+        <v>28.0855173534775</v>
       </c>
       <c r="B40" t="n">
-        <v>0.346572159724669</v>
+        <v>0.421553388194694</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.365414492764217</v>
+        <v>1.20630262326081</v>
       </c>
       <c r="B41" t="n">
-        <v>0.25807791934011</v>
+        <v>0.19192095535262</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.141717790401306</v>
+        <v>0.14410390123246</v>
       </c>
       <c r="B42" t="n">
-        <v>0.106239798439571</v>
+        <v>0.218478239401369</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>6.18959666349953</v>
+        <v>0.774778775872942</v>
       </c>
       <c r="B43" t="n">
-        <v>0.373484406601611</v>
+        <v>0.17984817144866</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.49631550336863</v>
+        <v>0.282962302129608</v>
       </c>
       <c r="B44" t="n">
-        <v>0.138901229541014</v>
+        <v>0.184169349023662</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.135083188376709</v>
+        <v>5.63130539200202</v>
       </c>
       <c r="B45" t="n">
-        <v>0.108691102917577</v>
+        <v>0.325079186461721</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>4.26001114179306</v>
+        <v>2.54808120358389</v>
       </c>
       <c r="B46" t="n">
-        <v>0.300243801294918</v>
+        <v>0.291462612181274</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>4.44313495466333</v>
+        <v>2.05351112264957</v>
       </c>
       <c r="B47" t="n">
-        <v>0.383124063346311</v>
+        <v>0.28270381895282</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2.34388460302478</v>
+        <v>0.137223307157266</v>
       </c>
       <c r="B48" t="n">
-        <v>0.250225643388903</v>
+        <v>0.0593085428478248</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.159655917155474</v>
+        <v>0.165681726450713</v>
       </c>
       <c r="B49" t="n">
-        <v>0.0919175772260024</v>
+        <v>0.0801573255385069</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.0278137195649074</v>
+        <v>1.4277304668247</v>
       </c>
       <c r="B50" t="n">
-        <v>0.0353391694174915</v>
+        <v>0.210090303148558</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.49841307209657</v>
+        <v>14.6908280240649</v>
       </c>
       <c r="B51" t="n">
-        <v>0.317447525583041</v>
+        <v>0.397101868146129</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>19.1130977728076</v>
+        <v>0.413791144230029</v>
       </c>
       <c r="B52" t="n">
-        <v>0.390767034384351</v>
+        <v>0.13237152958842</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>3.57352258822802</v>
+        <v>0.165049958995101</v>
       </c>
       <c r="B53" t="n">
-        <v>0.304598549870716</v>
+        <v>0.133126644298673</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>6.01361558127565</v>
+        <v>0.353520030665848</v>
       </c>
       <c r="B54" t="n">
-        <v>0.325618314156476</v>
+        <v>0.35615947271984</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1.43224472592171</v>
+        <v>3.80207737863589</v>
       </c>
       <c r="B55" t="n">
-        <v>0.205873163410096</v>
+        <v>0.288909516631005</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.131086329427266</v>
+        <v>2.02532722375782</v>
       </c>
       <c r="B56" t="n">
-        <v>0.231666263300079</v>
+        <v>0.252527801494932</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0.271418024559613</v>
+        <v>4.07589887836611</v>
       </c>
       <c r="B57" t="n">
-        <v>0.150702293386001</v>
+        <v>0.291367825581673</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1.44403213068365</v>
+        <v>5.30883221681596</v>
       </c>
       <c r="B58" t="n">
-        <v>0.332170305095964</v>
+        <v>0.314042871426703</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.0442500033157947</v>
+        <v>0.99988460780732</v>
       </c>
       <c r="B59" t="n">
-        <v>0.0481607377042202</v>
+        <v>0.1900724778763</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0.307714894012732</v>
+        <v>0.0529966315250405</v>
       </c>
       <c r="B60" t="n">
-        <v>0.356723852005285</v>
+        <v>0.0670249169839405</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>8.74929859862567</v>
+        <v>3.34386261065518</v>
       </c>
       <c r="B61" t="n">
-        <v>0.331509501129067</v>
+        <v>0.263529811080997</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1.52241366566281</v>
+        <v>3.57142902585491</v>
       </c>
       <c r="B62" t="n">
-        <v>0.354973651720257</v>
+        <v>0.268396490614302</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0.157911892400457</v>
+        <v>0.455412943652131</v>
       </c>
       <c r="B63" t="n">
-        <v>0.240411505114814</v>
+        <v>0.149278131526765</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0.0861459402978798</v>
+        <v>1.23704301200434</v>
       </c>
       <c r="B64" t="n">
-        <v>0.106169415880384</v>
+        <v>0.22714686428611</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0.182089420721175</v>
+        <v>0.144247644131004</v>
       </c>
       <c r="B65" t="n">
-        <v>0.290307765740475</v>
+        <v>0.083128166909741</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1.79679241584196</v>
+        <v>3.46982848702007</v>
       </c>
       <c r="B66" t="n">
-        <v>0.223935059666804</v>
+        <v>0.297395193710403</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.359202168248635</v>
+        <v>0.748436454720326</v>
       </c>
       <c r="B67" t="n">
-        <v>0.171573707717033</v>
+        <v>0.179674614089305</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>3.82251132301266</v>
+        <v>12.8435970743171</v>
       </c>
       <c r="B68" t="n">
-        <v>0.305359789075969</v>
+        <v>0.373422370869621</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0.048176081022873</v>
+        <v>3.14607259487208</v>
       </c>
       <c r="B69" t="n">
-        <v>0.0757837194200266</v>
+        <v>0.251019911898765</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0.175721651377786</v>
+        <v>0.631584219089361</v>
       </c>
       <c r="B70" t="n">
-        <v>0.221969985251344</v>
+        <v>0.174738542810904</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0.316283087169457</v>
+        <v>1.35650489042201</v>
       </c>
       <c r="B71" t="n">
-        <v>0.133539500719785</v>
+        <v>0.199580199354904</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.122517502266514</v>
+        <v>0.236475639093376</v>
       </c>
       <c r="B72" t="n">
-        <v>0.145347364361358</v>
+        <v>0.225189560598093</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0.706993653751413</v>
+        <v>1.28172056802641</v>
       </c>
       <c r="B73" t="n">
-        <v>0.170237743361561</v>
+        <v>0.194543585804354</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>0.655808898049165</v>
+        <v>0.0781199000044128</v>
       </c>
       <c r="B74" t="n">
-        <v>0.179916848377124</v>
+        <v>0.405349154541471</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0.575904022799445</v>
+        <v>0.813021984372275</v>
       </c>
       <c r="B75" t="n">
-        <v>0.151447446787215</v>
+        <v>0.156112366361114</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0.412172235115928</v>
+        <v>1.46906906988424</v>
       </c>
       <c r="B76" t="n">
-        <v>0.160305636366346</v>
+        <v>0.196056915028687</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.537996221217987</v>
+        <v>5.84348033687507</v>
       </c>
       <c r="B77" t="n">
-        <v>0.16505772855472</v>
+        <v>0.302156071128906</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0.435582095438148</v>
+        <v>1.50023088456315</v>
       </c>
       <c r="B78" t="n">
-        <v>0.160559526376908</v>
+        <v>0.251896769123029</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>0.302385171113479</v>
+        <v>0.135388294486145</v>
       </c>
       <c r="B79" t="n">
-        <v>0.131622264607313</v>
+        <v>0.0724255246008313</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>0.192928018979959</v>
+        <v>0.100380126541857</v>
       </c>
       <c r="B80" t="n">
-        <v>0.20304927115873</v>
+        <v>0.106269375067805</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>3.52955738281893</v>
+        <v>8.85108537047276</v>
       </c>
       <c r="B81" t="n">
-        <v>0.275965516198912</v>
+        <v>0.378864855361405</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1.12215475625981</v>
+        <v>1.55978497076994</v>
       </c>
       <c r="B82" t="n">
-        <v>0.255759211037178</v>
+        <v>0.259793544217213</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>0.645234244972727</v>
+        <v>0.149679741843972</v>
       </c>
       <c r="B83" t="n">
-        <v>0.17562269752542</v>
+        <v>0.0856722260720184</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>0.897050569053542</v>
+        <v>0.098333956653851</v>
       </c>
       <c r="B84" t="n">
-        <v>0.18130061760726</v>
+        <v>0.32022292431787</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>0.29711975851784</v>
+        <v>8.87536380021386</v>
       </c>
       <c r="B85" t="n">
-        <v>0.103299690748949</v>
+        <v>0.325074146856657</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>0.0595686423673833</v>
+        <v>9.39870423123835</v>
       </c>
       <c r="B86" t="n">
-        <v>0.042314422866419</v>
+        <v>0.358210670212383</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>0.117330437332212</v>
+        <v>1.34310736123803</v>
       </c>
       <c r="B87" t="n">
-        <v>0.0699237122373487</v>
+        <v>0.205214770969941</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>2.68848805287015</v>
+        <v>0.677575933498</v>
       </c>
       <c r="B88" t="n">
-        <v>0.294838519474349</v>
+        <v>0.155851059542789</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>0.0863566873652871</v>
+        <v>1.21192945721094</v>
       </c>
       <c r="B89" t="n">
-        <v>0.0678969612609211</v>
+        <v>0.182525372668356</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>0.685608971511709</v>
+        <v>0.0583272369480462</v>
       </c>
       <c r="B90" t="n">
-        <v>0.186433065111113</v>
+        <v>0.0559922522762049</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1.03819678698211</v>
+        <v>0.50537534395578</v>
       </c>
       <c r="B91" t="n">
-        <v>0.191293841849267</v>
+        <v>0.131345586139928</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>0.661554567653465</v>
+        <v>0.197899273888145</v>
       </c>
       <c r="B92" t="n">
-        <v>0.433356281290277</v>
+        <v>0.112717218287466</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>0.258429737578717</v>
+        <v>0.201577195444609</v>
       </c>
       <c r="B93" t="n">
-        <v>0.342477097830023</v>
+        <v>0.149840563725042</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>0.118955324276181</v>
+        <v>0.0526546602439452</v>
       </c>
       <c r="B94" t="n">
-        <v>0.282852328218799</v>
+        <v>0.0751578669968087</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>0.736374220622588</v>
+        <v>2.47122320130287</v>
       </c>
       <c r="B95" t="n">
-        <v>0.411949997186385</v>
+        <v>0.253328487523429</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>0.101243619998366</v>
+        <v>0.0809383808021505</v>
       </c>
       <c r="B96" t="n">
-        <v>0.259034372975242</v>
+        <v>0.0353871156683365</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>3.57184298314103</v>
+        <v>0.260467527142293</v>
       </c>
       <c r="B97" t="n">
-        <v>0.307895649399297</v>
+        <v>0.112497783328711</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>0.136460694535642</v>
+        <v>0.107648901412372</v>
       </c>
       <c r="B98" t="n">
-        <v>0.271475094054254</v>
+        <v>0.051674504686969</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>3.74231530621815</v>
+        <v>0.0403541303104529</v>
       </c>
       <c r="B99" t="n">
-        <v>0.303066685124989</v>
+        <v>0.0589788549164338</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1.08398448386781</v>
+        <v>0.0488522209960894</v>
       </c>
       <c r="B100" t="n">
-        <v>0.185500439728666</v>
+        <v>0.0625864957068522</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>0.179048946558028</v>
+        <v>0.381664939774372</v>
       </c>
       <c r="B101" t="n">
-        <v>0.0886917366393005</v>
+        <v>0.146904010338578</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1.80572649867466</v>
+        <v>2.54572165601366</v>
       </c>
       <c r="B104" t="n">
-        <v>0.227923676252751</v>
+        <v>0.199514197836077</v>
       </c>
     </row>
   </sheetData>
@@ -3984,18 +3987,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46016.8008357734</v>
+        <v>46026.0986146473</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
